--- a/trainingloadanalysis.xlsx
+++ b/trainingloadanalysis.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brooklynanderson/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1335C07-17EE-B641-8320-8D137361B81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AF3082-C03B-FA45-9028-6C8E874EBCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="15980" activeTab="3" xr2:uid="{0F7EC6E6-0350-AB43-B842-09780AAA44AE}"/>
   </bookViews>
   <sheets>
-    <sheet name="PivotTable" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="1" r:id="rId2"/>
-    <sheet name="Ranges" sheetId="2" r:id="rId3"/>
-    <sheet name="Dashboard" sheetId="3" r:id="rId4"/>
-    <sheet name="Calculator" sheetId="4" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="3" r:id="rId1"/>
+    <sheet name="PivotTable" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Calculator" sheetId="4" r:id="rId4"/>
+    <sheet name="Ranges" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Athlete">#N/A</definedName>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="24">
   <si>
     <t>Athlete</t>
   </si>
@@ -117,12 +117,24 @@
   <si>
     <t>Average of Training Load</t>
   </si>
+  <si>
+    <t>Training Load Calculator</t>
+  </si>
+  <si>
+    <t>Duration (Mins)</t>
+  </si>
+  <si>
+    <t>RPE (1-10)</t>
+  </si>
+  <si>
+    <t>Training Load (AU)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -130,16 +142,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -147,11 +191,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -161,11 +295,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -198,6 +413,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC7C637"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -210,719 +430,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[trainingloadanalysis.xlsx]PivotTable!PivotTable1</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-CA" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Average Training Load by Session Type</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.11331653989452609"/>
-          <c:y val="8.5425263602471935E-2"/>
-          <c:w val="0.83233776293451756"/>
-          <c:h val="0.76324387428894735"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>PivotTable!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>PivotTable!$A$4:$A$16</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="10"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Conditioning</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Game</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Lift</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Recovery</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Skate</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Conditioning</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>Game</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>Lift</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Recovery</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>Skate</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Athlete 1</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Athlete 2</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>PivotTable!$B$4:$B$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>580</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>832.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>262.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>411.66666666666669</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>620</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>819</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>285</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>431.66666666666669</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1126-C741-8FEA-D3D76D701881}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="1134088943"/>
-        <c:axId val="1133636895"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1134088943"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="1">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Session </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> Type</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US" sz="1200" b="1">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:endParaRPr>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1133636895"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1133636895"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="1">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Average</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> Training Load (AU)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US" sz="1200" b="1">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:endParaRPr>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="1.0732037243778435E-2"/>
-              <c:y val="0.34973452706504654"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1134088943"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1733,6 +1240,719 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[trainingloadanalysis.xlsx]PivotTable!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-CA" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Average Training Load by Session Type</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11331653989452609"/>
+          <c:y val="8.5425263602471935E-2"/>
+          <c:w val="0.83233776293451756"/>
+          <c:h val="0.76324387428894735"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTable!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>PivotTable!$A$4:$A$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="10"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Conditioning</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Game</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Lift</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Recovery</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Skate</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Conditioning</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Game</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Lift</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Recovery</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Skate</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Athlete 1</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Athlete 2</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTable!$B$4:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>832.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>262.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>411.66666666666669</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>819</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>431.66666666666669</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1126-C741-8FEA-D3D76D701881}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1134088943"/>
+        <c:axId val="1133636895"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1134088943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Session </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> Type</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1133636895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1133636895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> Training Load (AU)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.0732037243778435E-2"/>
+              <c:y val="0.34973452706504654"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1134088943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2820,203 +3040,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>12699</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>180972</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="Athlete">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F73F4C5F-E56E-E6B5-0700-E52A7A360674}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Athlete"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6384878" y="417015"/>
-              <a:ext cx="1854389" cy="2683061"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>180972</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Session Type">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{079DC076-025E-4C31-F45C-014E72A225F7}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Session Type"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6946900" y="406400"/>
-              <a:ext cx="1828800" cy="2619372"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>151641</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39827896-A84E-0670-7BA2-46D8975AA551}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3210,6 +3233,203 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12699</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180972</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Athlete">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F73F4C5F-E56E-E6B5-0700-E52A7A360674}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Athlete"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6384878" y="417015"/>
+              <a:ext cx="1854389" cy="2683061"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180972</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Session Type">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{079DC076-025E-4C31-F45C-014E72A225F7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Session Type"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6946900" y="406400"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>151641</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39827896-A84E-0670-7BA2-46D8975AA551}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3695,15 +3915,15 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Athlete" xr10:uid="{8F5291CE-5224-7049-B03A-FB03BB8DA8BB}" cache="Slicer_Athlete" caption="Athlete" style="SlicerStyleOther2" rowHeight="251883"/>
-  <slicer name="Session Type" xr10:uid="{1D02C209-90DB-DA49-8C67-3D0E4A1C6BFD}" cache="Slicer_Session_Type" caption="Session Type" style="SlicerStyleOther2" rowHeight="251883"/>
+  <slicer name="Athlete 1" xr10:uid="{201BCFA6-DA00-1A45-8AA5-A3DD44967EA9}" cache="Slicer_Athlete" caption="Athlete" style="SlicerStyleDark4" rowHeight="251883"/>
+  <slicer name="Session Type 1" xr10:uid="{1D76F50B-1E6E-0F41-A2B1-1E82E52D7417}" cache="Slicer_Session_Type" caption="Session Type" style="SlicerStyleDark4" rowHeight="251883"/>
 </slicers>
 </file>
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Athlete 1" xr10:uid="{201BCFA6-DA00-1A45-8AA5-A3DD44967EA9}" cache="Slicer_Athlete" caption="Athlete" style="SlicerStyleDark4" rowHeight="251883"/>
-  <slicer name="Session Type 1" xr10:uid="{1D76F50B-1E6E-0F41-A2B1-1E82E52D7417}" cache="Slicer_Session_Type" caption="Session Type" style="SlicerStyleDark4" rowHeight="251883"/>
+  <slicer name="Athlete" xr10:uid="{8F5291CE-5224-7049-B03A-FB03BB8DA8BB}" cache="Slicer_Athlete" caption="Athlete" style="SlicerStyleOther2" rowHeight="251883"/>
+  <slicer name="Session Type" xr10:uid="{1D02C209-90DB-DA49-8C67-3D0E4A1C6BFD}" cache="Slicer_Session_Type" caption="Session Type" style="SlicerStyleOther2" rowHeight="251883"/>
 </slicers>
 </file>
 
@@ -4047,6 +4267,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CABC2AE1-BB59-A343-9A7A-52CB8E562419}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC5107B-5D98-5944-B087-A139773BDD90}">
   <dimension ref="A3:B16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4180,7 +4417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{390DFED9-AB43-7641-BC40-BDB4A087BF63}">
   <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5025,13 +5262,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I26">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Moderate">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Moderate">
       <formula>NOT(ISERROR(SEARCH("Moderate",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5054,7 +5291,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE76EB56-2FA1-BA40-ACDC-5495D4097E64}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="13"/>
+    </row>
+    <row r="2" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="11">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="6"/>
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="10">
+        <f>B3*B4</f>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9" t="str">
+        <f>IF(B6&lt;300,"Low",IF(B6&lt;=600,"Moderate","High"))</f>
+        <v>Moderate</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",B7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Moderate">
+      <formula>NOT(ISERROR(SEARCH("Moderate",B7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",B7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B3DE43-2A6B-EF44-ADFD-AE6ECF98A954}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5095,30 +5404,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CABC2AE1-BB59-A343-9A7A-52CB8E562419}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
-      <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE76EB56-2FA1-BA40-ACDC-5495D4097E64}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>